--- a/data/DRM Rapid Screening Tool - Questionnaire.xlsx
+++ b/data/DRM Rapid Screening Tool - Questionnaire.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="82">
   <si>
     <t xml:space="preserve">Evaluating Disaster Risk Management Policy Frameworks: A Rapid Screening Tool</t>
   </si>
@@ -55,74 +55,12 @@
     <t xml:space="preserve">Question</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Answer 
-(Yes / No / Partially / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Unknown</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Source
-(include electronic links to s</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">upporting documents</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> when available)</t>
-    </r>
+    <t xml:space="preserve">Answer 
+(Yes / No / Partially / Unknown)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source
+(include electronic links to supporting documents when available)</t>
   </si>
   <si>
     <t xml:space="preserve">Notes / Comments</t>
@@ -149,6 +87,9 @@
     <t xml:space="preserve">Is there a legal framework (e.g., a DRM law or other legally-binding instruments) defining distinct responsibilities for disaster risk reduction and emergency management?</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Have any implementing decrees or regulations been approved since the adoption of the DRM legal framework? (e.g., rules on the structure or functions of the DRM agency or implementing regulations of the DRM law)</t>
   </si>
   <si>
@@ -240,6 +181,9 @@
   </si>
   <si>
     <t xml:space="preserve">Have any watershed basins undergone improvements in water management in the last four years?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partially</t>
   </si>
   <si>
     <t xml:space="preserve">4. Preparedness</t>
@@ -333,7 +277,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,13 +373,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
@@ -543,20 +480,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -568,59 +509,47 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -636,7 +565,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -648,7 +577,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -660,19 +589,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -680,15 +609,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -696,19 +625,15 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -774,7 +699,7 @@
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF46B1E1"/>
+      <rgbColor rgb="FF45B1E1"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
@@ -974,1489 +899,1552 @@
   <dimension ref="B1:BA197"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="89.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="40.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="23.67"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="8" min="8" style="3" width="9.49"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="9" style="2" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="11" style="3" width="17.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="28.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="89.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="31.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="40.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="23.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="8" min="8" style="4" width="9.49"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="9" style="3" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="11" style="4" width="17.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="28.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="20.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
+      <c r="B4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="8"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="8"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="18"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18"/>
-      <c r="V8" s="18"/>
-      <c r="W8" s="18"/>
-      <c r="X8" s="18"/>
-      <c r="Y8" s="18"/>
-      <c r="Z8" s="18"/>
-      <c r="AA8" s="18"/>
-      <c r="AB8" s="18"/>
-      <c r="AC8" s="18"/>
-      <c r="AD8" s="18"/>
-      <c r="AE8" s="18"/>
-      <c r="AF8" s="18"/>
-      <c r="AG8" s="18"/>
-      <c r="AH8" s="18"/>
-      <c r="AI8" s="18"/>
-      <c r="AJ8" s="18"/>
-      <c r="AK8" s="18"/>
-      <c r="AL8" s="18"/>
-      <c r="AM8" s="18"/>
-      <c r="AN8" s="18"/>
-      <c r="AO8" s="18"/>
-      <c r="AP8" s="18"/>
-      <c r="AQ8" s="18"/>
-      <c r="AR8" s="18"/>
-      <c r="AS8" s="18"/>
-      <c r="AT8" s="18"/>
-      <c r="AU8" s="18"/>
-      <c r="AV8" s="18"/>
-      <c r="AW8" s="18"/>
-      <c r="AX8" s="18"/>
-      <c r="AY8" s="18"/>
-      <c r="AZ8" s="18"/>
-      <c r="BA8" s="18"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="16"/>
+      <c r="AI8" s="16"/>
+      <c r="AJ8" s="16"/>
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="16"/>
+      <c r="AM8" s="16"/>
+      <c r="AN8" s="16"/>
+      <c r="AO8" s="16"/>
+      <c r="AP8" s="16"/>
+      <c r="AQ8" s="16"/>
+      <c r="AR8" s="16"/>
+      <c r="AS8" s="16"/>
+      <c r="AT8" s="16"/>
+      <c r="AU8" s="16"/>
+      <c r="AV8" s="16"/>
+      <c r="AW8" s="16"/>
+      <c r="AX8" s="16"/>
+      <c r="AY8" s="16"/>
+      <c r="AZ8" s="16"/>
+      <c r="BA8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="18"/>
-      <c r="V9" s="18"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="18"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="18"/>
-      <c r="AA9" s="18"/>
-      <c r="AB9" s="18"/>
-      <c r="AC9" s="18"/>
-      <c r="AD9" s="18"/>
-      <c r="AE9" s="18"/>
-      <c r="AF9" s="18"/>
-      <c r="AG9" s="18"/>
-      <c r="AH9" s="18"/>
-      <c r="AI9" s="18"/>
-      <c r="AJ9" s="18"/>
-      <c r="AK9" s="18"/>
-      <c r="AL9" s="18"/>
-      <c r="AM9" s="18"/>
-      <c r="AN9" s="18"/>
-      <c r="AO9" s="18"/>
-      <c r="AP9" s="18"/>
-      <c r="AQ9" s="18"/>
-      <c r="AR9" s="18"/>
-      <c r="AS9" s="18"/>
-      <c r="AT9" s="18"/>
-      <c r="AU9" s="18"/>
-      <c r="AV9" s="18"/>
-      <c r="AW9" s="18"/>
-      <c r="AX9" s="18"/>
-      <c r="AY9" s="18"/>
-      <c r="AZ9" s="18"/>
-      <c r="BA9" s="18"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="16"/>
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="16"/>
+      <c r="AM9" s="16"/>
+      <c r="AN9" s="16"/>
+      <c r="AO9" s="16"/>
+      <c r="AP9" s="16"/>
+      <c r="AQ9" s="16"/>
+      <c r="AR9" s="16"/>
+      <c r="AS9" s="16"/>
+      <c r="AT9" s="16"/>
+      <c r="AU9" s="16"/>
+      <c r="AV9" s="16"/>
+      <c r="AW9" s="16"/>
+      <c r="AX9" s="16"/>
+      <c r="AY9" s="16"/>
+      <c r="AZ9" s="16"/>
+      <c r="BA9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20" t="str">
+      <c r="B10" s="18" t="str">
         <f aca="false">IF(COUNTBLANK(E15:E60)&gt;0,_xlfn.CONCAT("Please complete the assessment to proceed. Remaining questions: ",COUNTBLANK(E15:E60)), _xlfn.TEXTJOIN("&amp;",FALSE(),K15:K60))</f>
-        <v>Please complete the assessment to proceed. Remaining questions: 46</v>
-      </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="15" t="s">
+        <v>Q1;Yes;1&amp;Q2;Yes;1&amp;Q3;Yes;1&amp;Q4;Yes;1&amp;Q5;Yes;1&amp;Q6;Yes;1&amp;Q7;Yes;1&amp;Q8;Yes;1&amp;Q9;Yes;1&amp;Q10;Yes;1&amp;Q11;Yes;1&amp;Q12;Yes;1&amp;Q13;Yes;1&amp;Q14;Yes;1&amp;Q15;Yes;1&amp;Q16;Yes;1&amp;Q17;Yes;1&amp;Q18;Yes;0.25&amp;Q19;Yes;0.25&amp;Q20;Yes;0.25&amp;Q21;Yes;0.25&amp;Q22;Yes;1&amp;Q23;Yes;1&amp;Q24;Yes;1&amp;Q25;Yes;1&amp;Q26;Partially;1&amp;Q27;Partially;1&amp;Q28;Yes;1&amp;Q29;Yes;1&amp;Q30;Yes;1&amp;Q31;Yes;1&amp;Q32;Yes;1&amp;Q33;Yes;1&amp;Q34;Yes;1&amp;Q35;Yes;1&amp;Q36;Yes;1&amp;Q37;Yes;1&amp;Q38;Yes;1&amp;Q39;Yes;1&amp;Q40;Yes;1&amp;Q41;Yes;1&amp;Q42;Yes;1&amp;Q43;Yes;1&amp;Q44;Yes;1&amp;Q45;Yes;1&amp;Q46;Yes;1</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="18"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="18"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="18"/>
-      <c r="Y10" s="18"/>
-      <c r="Z10" s="18"/>
-      <c r="AA10" s="18"/>
-      <c r="AB10" s="18"/>
-      <c r="AC10" s="18"/>
-      <c r="AD10" s="18"/>
-      <c r="AE10" s="18"/>
-      <c r="AF10" s="18"/>
-      <c r="AG10" s="18"/>
-      <c r="AH10" s="18"/>
-      <c r="AI10" s="18"/>
-      <c r="AJ10" s="18"/>
-      <c r="AK10" s="18"/>
-      <c r="AL10" s="18"/>
-      <c r="AM10" s="18"/>
-      <c r="AN10" s="18"/>
-      <c r="AO10" s="18"/>
-      <c r="AP10" s="18"/>
-      <c r="AQ10" s="18"/>
-      <c r="AR10" s="18"/>
-      <c r="AS10" s="18"/>
-      <c r="AT10" s="18"/>
-      <c r="AU10" s="18"/>
-      <c r="AV10" s="18"/>
-      <c r="AW10" s="18"/>
-      <c r="AX10" s="18"/>
-      <c r="AY10" s="18"/>
-      <c r="AZ10" s="18"/>
-      <c r="BA10" s="18"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="16"/>
+      <c r="AG10" s="16"/>
+      <c r="AH10" s="16"/>
+      <c r="AI10" s="16"/>
+      <c r="AJ10" s="16"/>
+      <c r="AK10" s="16"/>
+      <c r="AL10" s="16"/>
+      <c r="AM10" s="16"/>
+      <c r="AN10" s="16"/>
+      <c r="AO10" s="16"/>
+      <c r="AP10" s="16"/>
+      <c r="AQ10" s="16"/>
+      <c r="AR10" s="16"/>
+      <c r="AS10" s="16"/>
+      <c r="AT10" s="16"/>
+      <c r="AU10" s="16"/>
+      <c r="AV10" s="16"/>
+      <c r="AW10" s="16"/>
+      <c r="AX10" s="16"/>
+      <c r="AY10" s="16"/>
+      <c r="AZ10" s="16"/>
+      <c r="BA10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="11"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
+      <c r="B11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+      <c r="B13" s="10"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="45.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="25" t="s">
+      <c r="I14" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="25" t="s">
+      <c r="K14" s="23" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="28" t="str">
+      <c r="E15" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I15)</f>
         <v>Q1</v>
       </c>
-      <c r="K15" s="29" t="str">
+      <c r="K15" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J15,E15,H15)</f>
-        <v>Q1;;1</v>
+        <v>Q1;Yes;1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="32" t="n">
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="30" t="n">
         <f aca="false">I15+1</f>
         <v>2</v>
       </c>
-      <c r="J16" s="33" t="str">
+      <c r="J16" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I16)</f>
         <v>Q2</v>
       </c>
-      <c r="K16" s="31" t="str">
+      <c r="K16" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J16,E16,H16)</f>
-        <v>Q2;;1</v>
-      </c>
-      <c r="L16" s="34"/>
+        <v>Q2;Yes;1</v>
+      </c>
+      <c r="L16" s="32"/>
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="29" t="n">
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="27" t="n">
         <f aca="false">I16+1</f>
         <v>3</v>
       </c>
-      <c r="J17" s="28" t="str">
+      <c r="J17" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I17)</f>
         <v>Q3</v>
       </c>
-      <c r="K17" s="29" t="str">
+      <c r="K17" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J17,E17,H17)</f>
-        <v>Q3;;1</v>
+        <v>Q3;Yes;1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="32" t="n">
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="30" t="n">
         <f aca="false">I17+1</f>
         <v>4</v>
       </c>
-      <c r="J18" s="33" t="str">
+      <c r="J18" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I18)</f>
         <v>Q4</v>
       </c>
-      <c r="K18" s="31" t="str">
+      <c r="K18" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J18,E18,H18)</f>
-        <v>Q4;;1</v>
+        <v>Q4;Yes;1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="26"/>
-      <c r="C19" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="27" t="s">
+      <c r="B19" s="24"/>
+      <c r="C19" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="29" t="n">
+      <c r="D19" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="27" t="n">
         <f aca="false">I18+1</f>
         <v>5</v>
       </c>
-      <c r="J19" s="28" t="str">
+      <c r="J19" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I19)</f>
         <v>Q5</v>
       </c>
-      <c r="K19" s="29" t="str">
+      <c r="K19" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J19,E19,H19)</f>
-        <v>Q5;;1</v>
+        <v>Q5;Yes;1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="32" t="n">
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="30" t="n">
         <f aca="false">I19+1</f>
         <v>6</v>
       </c>
-      <c r="J20" s="33" t="str">
+      <c r="J20" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I20)</f>
         <v>Q6</v>
       </c>
-      <c r="K20" s="31" t="str">
+      <c r="K20" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J20,E20,H20)</f>
-        <v>Q6;;1</v>
-      </c>
-      <c r="L20" s="35"/>
+        <v>Q6;Yes;1</v>
+      </c>
+      <c r="L20" s="33"/>
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="27" t="s">
+      <c r="B21" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="29" t="n">
+      <c r="C21" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="27" t="n">
         <f aca="false">I20+1</f>
         <v>7</v>
       </c>
-      <c r="J21" s="28" t="str">
+      <c r="J21" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I21)</f>
         <v>Q7</v>
       </c>
-      <c r="K21" s="29" t="str">
+      <c r="K21" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J21,E21,H21)</f>
-        <v>Q7;;1</v>
+        <v>Q7;Yes;1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="32" t="n">
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="30" t="n">
         <f aca="false">I21+1</f>
         <v>8</v>
       </c>
-      <c r="J22" s="33" t="str">
+      <c r="J22" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I22)</f>
         <v>Q8</v>
       </c>
-      <c r="K22" s="31" t="str">
+      <c r="K22" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J22,E22,H22)</f>
-        <v>Q8;;1</v>
+        <v>Q8;Yes;1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="29" t="n">
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="27" t="n">
         <f aca="false">I22+1</f>
         <v>9</v>
       </c>
-      <c r="J23" s="28" t="str">
+      <c r="J23" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I23)</f>
         <v>Q9</v>
       </c>
-      <c r="K23" s="29" t="str">
+      <c r="K23" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J23,E23,H23)</f>
-        <v>Q9;;1</v>
-      </c>
-      <c r="L23" s="34"/>
+        <v>Q9;Yes;1</v>
+      </c>
+      <c r="L23" s="32"/>
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="32" t="n">
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="30" t="n">
         <f aca="false">I23+1</f>
         <v>10</v>
       </c>
-      <c r="J24" s="33" t="str">
+      <c r="J24" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I24)</f>
         <v>Q10</v>
       </c>
-      <c r="K24" s="31" t="str">
+      <c r="K24" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J24,E24,H24)</f>
-        <v>Q10;;1</v>
+        <v>Q10;Yes;1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="26" t="s">
+      <c r="B25" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="C25" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="29" t="n">
+      <c r="D25" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="27" t="n">
         <f aca="false">I24+1</f>
         <v>11</v>
       </c>
-      <c r="J25" s="28" t="str">
+      <c r="J25" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I25)</f>
         <v>Q11</v>
       </c>
-      <c r="K25" s="29" t="str">
+      <c r="K25" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J25,E25,H25)</f>
-        <v>Q11;;1</v>
+        <v>Q11;Yes;1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="32" t="n">
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="30" t="n">
         <f aca="false">I25+1</f>
         <v>12</v>
       </c>
-      <c r="J26" s="33" t="str">
+      <c r="J26" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I26)</f>
         <v>Q12</v>
       </c>
-      <c r="K26" s="31" t="str">
+      <c r="K26" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J26,E26,H26)</f>
-        <v>Q12;;1</v>
+        <v>Q12;Yes;1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="29" t="n">
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="27" t="n">
         <f aca="false">I26+1</f>
         <v>13</v>
       </c>
-      <c r="J27" s="28" t="str">
+      <c r="J27" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I27)</f>
         <v>Q13</v>
       </c>
-      <c r="K27" s="29" t="str">
+      <c r="K27" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J27,E27,H27)</f>
-        <v>Q13;;1</v>
+        <v>Q13;Yes;1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="32" t="n">
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="30" t="n">
         <f aca="false">I27+1</f>
         <v>14</v>
       </c>
-      <c r="J28" s="33" t="str">
+      <c r="J28" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I28)</f>
         <v>Q14</v>
       </c>
-      <c r="K28" s="31" t="str">
+      <c r="K28" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J28,E28,H28)</f>
-        <v>Q14;;1</v>
-      </c>
-      <c r="L28" s="34"/>
+        <v>Q14;Yes;1</v>
+      </c>
+      <c r="L28" s="32"/>
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="26"/>
-      <c r="C29" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="27" t="s">
+      <c r="B29" s="24"/>
+      <c r="C29" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="29" t="n">
+      <c r="D29" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="27" t="n">
         <f aca="false">I28+1</f>
         <v>15</v>
       </c>
-      <c r="J29" s="28" t="str">
+      <c r="J29" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I29)</f>
         <v>Q15</v>
       </c>
-      <c r="K29" s="29" t="str">
+      <c r="K29" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J29,E29,H29)</f>
-        <v>Q15;;1</v>
+        <v>Q15;Yes;1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="32" t="n">
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="30" t="n">
         <f aca="false">I29+1</f>
         <v>16</v>
       </c>
-      <c r="J30" s="33" t="str">
+      <c r="J30" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I30)</f>
         <v>Q16</v>
       </c>
-      <c r="K30" s="31" t="str">
+      <c r="K30" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J30,E30,H30)</f>
-        <v>Q16;;1</v>
+        <v>Q16;Yes;1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="29" t="n">
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="27" t="n">
         <f aca="false">I30+1</f>
         <v>17</v>
       </c>
-      <c r="J31" s="28" t="str">
+      <c r="J31" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I31)</f>
         <v>Q17</v>
       </c>
-      <c r="K31" s="29" t="str">
+      <c r="K31" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J31,E31,H31)</f>
-        <v>Q17;;1</v>
-      </c>
-      <c r="L31" s="36"/>
+        <v>Q17;Yes;1</v>
+      </c>
+      <c r="L31" s="34"/>
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="26"/>
-      <c r="C32" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="26" t="s">
+      <c r="B32" s="24"/>
+      <c r="C32" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="32" t="n">
+      <c r="D32" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="30" t="n">
         <v>0.25</v>
       </c>
-      <c r="I32" s="32" t="n">
+      <c r="I32" s="30" t="n">
         <f aca="false">I31+1</f>
         <v>18</v>
       </c>
-      <c r="J32" s="33" t="str">
+      <c r="J32" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I32)</f>
         <v>Q18</v>
       </c>
-      <c r="K32" s="31" t="str">
+      <c r="K32" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J32,E32,H32)</f>
-        <v>Q18;;0.25</v>
+        <v>Q18;Yes;0.25</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28" t="n">
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26" t="n">
         <v>0.25</v>
       </c>
-      <c r="I33" s="29" t="n">
+      <c r="I33" s="27" t="n">
         <f aca="false">I32+1</f>
         <v>19</v>
       </c>
-      <c r="J33" s="28" t="str">
+      <c r="J33" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I33)</f>
         <v>Q19</v>
       </c>
-      <c r="K33" s="29" t="str">
+      <c r="K33" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J33,E33,H33)</f>
-        <v>Q19;;0.25</v>
+        <v>Q19;Yes;0.25</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="32" t="n">
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="30" t="n">
         <v>0.25</v>
       </c>
-      <c r="I34" s="32" t="n">
+      <c r="I34" s="30" t="n">
         <f aca="false">I33+1</f>
         <v>20</v>
       </c>
-      <c r="J34" s="33" t="str">
+      <c r="J34" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I34)</f>
         <v>Q20</v>
       </c>
-      <c r="K34" s="31" t="str">
+      <c r="K34" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J34,E34,H34)</f>
-        <v>Q20;;0.25</v>
+        <v>Q20;Yes;0.25</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28" t="n">
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26" t="n">
         <v>0.25</v>
       </c>
-      <c r="I35" s="29" t="n">
+      <c r="I35" s="27" t="n">
         <f aca="false">I34+1</f>
         <v>21</v>
       </c>
-      <c r="J35" s="28" t="str">
+      <c r="J35" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I35)</f>
         <v>Q21</v>
       </c>
-      <c r="K35" s="29" t="str">
+      <c r="K35" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J35,E35,H35)</f>
-        <v>Q21;;0.25</v>
+        <v>Q21;Yes;0.25</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="32" t="n">
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="30" t="n">
         <f aca="false">I35+1</f>
         <v>22</v>
       </c>
-      <c r="J36" s="33" t="str">
+      <c r="J36" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I36)</f>
         <v>Q22</v>
       </c>
-      <c r="K36" s="31" t="str">
+      <c r="K36" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J36,E36,H36)</f>
-        <v>Q22;;1</v>
+        <v>Q22;Yes;1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="29" t="n">
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="27" t="n">
         <f aca="false">I36+1</f>
         <v>23</v>
       </c>
-      <c r="J37" s="28" t="str">
+      <c r="J37" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I37)</f>
         <v>Q23</v>
       </c>
-      <c r="K37" s="29" t="str">
+      <c r="K37" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J37,E37,H37)</f>
-        <v>Q23;;1</v>
+        <v>Q23;Yes;1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="32" t="n">
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="30" t="n">
         <f aca="false">I37+1</f>
         <v>24</v>
       </c>
-      <c r="J38" s="33" t="str">
+      <c r="J38" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I38)</f>
         <v>Q24</v>
       </c>
-      <c r="K38" s="31" t="str">
+      <c r="K38" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J38,E38,H38)</f>
-        <v>Q24;;1</v>
+        <v>Q24;Yes;1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="29" t="n">
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="27" t="n">
         <f aca="false">I38+1</f>
         <v>25</v>
       </c>
-      <c r="J39" s="28" t="str">
+      <c r="J39" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I39)</f>
         <v>Q25</v>
       </c>
-      <c r="K39" s="29" t="str">
+      <c r="K39" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J39,E39,H39)</f>
-        <v>Q25;;1</v>
+        <v>Q25;Yes;1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="32" t="n">
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="30" t="n">
         <f aca="false">I39+1</f>
         <v>26</v>
       </c>
-      <c r="J40" s="33" t="str">
+      <c r="J40" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I40)</f>
         <v>Q26</v>
       </c>
-      <c r="K40" s="31" t="str">
+      <c r="K40" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J40,E40,H40)</f>
-        <v>Q26;;1</v>
+        <v>Q26;Partially;1</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="C41" s="26" t="s">
+      <c r="B41" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D41" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="29" t="n">
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="27" t="n">
         <f aca="false">I40+1</f>
         <v>27</v>
       </c>
-      <c r="J41" s="28" t="str">
+      <c r="J41" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I41)</f>
         <v>Q27</v>
       </c>
-      <c r="K41" s="29" t="str">
+      <c r="K41" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J41,E41,H41)</f>
-        <v>Q27;;1</v>
+        <v>Q27;Partially;1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="40"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="32" t="n">
+      <c r="B42" s="37"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="30" t="n">
         <f aca="false">I41+1</f>
         <v>28</v>
       </c>
-      <c r="J42" s="33" t="str">
+      <c r="J42" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I42)</f>
         <v>Q28</v>
       </c>
-      <c r="K42" s="31" t="str">
+      <c r="K42" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J42,E42,H42)</f>
-        <v>Q28;;1</v>
+        <v>Q28;Yes;1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="40"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="29" t="n">
+      <c r="B43" s="37"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="27" t="n">
         <f aca="false">I42+1</f>
         <v>29</v>
       </c>
-      <c r="J43" s="28" t="str">
+      <c r="J43" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I43)</f>
         <v>Q29</v>
       </c>
-      <c r="K43" s="29" t="str">
+      <c r="K43" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J43,E43,H43)</f>
-        <v>Q29;;1</v>
+        <v>Q29;Yes;1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="40"/>
-      <c r="C44" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" s="42" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="32" t="n">
+      <c r="B44" s="37"/>
+      <c r="C44" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="30" t="n">
         <f aca="false">I43+1</f>
         <v>30</v>
       </c>
-      <c r="J44" s="33" t="str">
+      <c r="J44" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I44)</f>
         <v>Q30</v>
       </c>
-      <c r="K44" s="31" t="str">
+      <c r="K44" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J44,E44,H44)</f>
-        <v>Q30;;1</v>
+        <v>Q30;Yes;1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="40"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="29" t="n">
+      <c r="B45" s="37"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="27" t="n">
         <f aca="false">I44+1</f>
         <v>31</v>
       </c>
-      <c r="J45" s="28" t="str">
+      <c r="J45" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I45)</f>
         <v>Q31</v>
       </c>
-      <c r="K45" s="29" t="str">
+      <c r="K45" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J45,E45,H45)</f>
-        <v>Q31;;1</v>
+        <v>Q31;Yes;1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="40"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="32" t="n">
+      <c r="B46" s="37"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="30" t="n">
         <f aca="false">I45+1</f>
         <v>32</v>
       </c>
-      <c r="J46" s="33" t="str">
+      <c r="J46" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I46)</f>
         <v>Q32</v>
       </c>
-      <c r="K46" s="31" t="str">
+      <c r="K46" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J46,E46,H46)</f>
-        <v>Q32;;1</v>
+        <v>Q32;Yes;1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="40"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" s="29" t="n">
+      <c r="B47" s="37"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="27" t="n">
         <f aca="false">I46+1</f>
         <v>33</v>
       </c>
-      <c r="J47" s="28" t="str">
+      <c r="J47" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I47)</f>
         <v>Q33</v>
       </c>
-      <c r="K47" s="29" t="str">
+      <c r="K47" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J47,E47,H47)</f>
-        <v>Q33;;1</v>
+        <v>Q33;Yes;1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="40"/>
-      <c r="C48" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" s="32" t="n">
+      <c r="B48" s="37"/>
+      <c r="C48" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E48" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="30" t="n">
         <f aca="false">I47+1</f>
         <v>34</v>
       </c>
-      <c r="J48" s="33" t="str">
+      <c r="J48" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I48)</f>
         <v>Q34</v>
       </c>
-      <c r="K48" s="31" t="str">
+      <c r="K48" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J48,E48,H48)</f>
-        <v>Q34;;1</v>
+        <v>Q34;Yes;1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="40"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" s="29" t="n">
+      <c r="B49" s="37"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="27" t="n">
         <f aca="false">I48+1</f>
         <v>35</v>
       </c>
-      <c r="J49" s="28" t="str">
+      <c r="J49" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I49)</f>
         <v>Q35</v>
       </c>
-      <c r="K49" s="29" t="str">
+      <c r="K49" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J49,E49,H49)</f>
-        <v>Q35;;1</v>
+        <v>Q35;Yes;1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="40"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="32" t="n">
+      <c r="B50" s="37"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="30" t="n">
         <f aca="false">I49+1</f>
         <v>36</v>
       </c>
-      <c r="J50" s="33" t="str">
+      <c r="J50" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I50)</f>
         <v>Q36</v>
       </c>
-      <c r="K50" s="31" t="str">
+      <c r="K50" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J50,E50,H50)</f>
-        <v>Q36;;1</v>
+        <v>Q36;Yes;1</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="D51" s="41" t="s">
+      <c r="B51" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="29" t="n">
+      <c r="C51" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="27" t="n">
         <f aca="false">I50+1</f>
         <v>37</v>
       </c>
-      <c r="J51" s="28" t="str">
+      <c r="J51" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I51)</f>
         <v>Q37</v>
       </c>
-      <c r="K51" s="29" t="str">
+      <c r="K51" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J51,E51,H51)</f>
-        <v>Q37;;1</v>
+        <v>Q37;Yes;1</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="40"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="32" t="n">
+      <c r="B52" s="37"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E52" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="30" t="n">
         <f aca="false">I51+1</f>
         <v>38</v>
       </c>
-      <c r="J52" s="33" t="str">
+      <c r="J52" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I52)</f>
         <v>Q38</v>
       </c>
-      <c r="K52" s="31" t="str">
+      <c r="K52" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J52,E52,H52)</f>
-        <v>Q38;;1</v>
+        <v>Q38;Yes;1</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="40"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" s="29" t="n">
+      <c r="B53" s="37"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="E53" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="27" t="n">
         <f aca="false">I52+1</f>
         <v>39</v>
       </c>
-      <c r="J53" s="28" t="str">
+      <c r="J53" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I53)</f>
         <v>Q39</v>
       </c>
-      <c r="K53" s="29" t="str">
+      <c r="K53" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J53,E53,H53)</f>
-        <v>Q39;;1</v>
+        <v>Q39;Yes;1</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="40"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" s="32" t="n">
+      <c r="B54" s="37"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="30" t="n">
         <f aca="false">I53+1</f>
         <v>40</v>
       </c>
-      <c r="J54" s="33" t="str">
+      <c r="J54" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I54)</f>
         <v>Q40</v>
       </c>
-      <c r="K54" s="31" t="str">
+      <c r="K54" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J54,E54,H54)</f>
-        <v>Q40;;1</v>
+        <v>Q40;Yes;1</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="40"/>
-      <c r="C55" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D55" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" s="29" t="n">
+      <c r="B55" s="37"/>
+      <c r="C55" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D55" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="27" t="n">
         <f aca="false">I54+1</f>
         <v>41</v>
       </c>
-      <c r="J55" s="28" t="str">
+      <c r="J55" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I55)</f>
         <v>Q41</v>
       </c>
-      <c r="K55" s="29" t="str">
+      <c r="K55" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J55,E55,H55)</f>
-        <v>Q41;;1</v>
+        <v>Q41;Yes;1</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="40"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" s="32" t="n">
+      <c r="B56" s="37"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="30" t="n">
         <f aca="false">I55+1</f>
         <v>42</v>
       </c>
-      <c r="J56" s="33" t="str">
+      <c r="J56" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I56)</f>
         <v>Q42</v>
       </c>
-      <c r="K56" s="31" t="str">
+      <c r="K56" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J56,E56,H56)</f>
-        <v>Q42;;1</v>
+        <v>Q42;Yes;1</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="40"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I57" s="29" t="n">
+      <c r="B57" s="37"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="27" t="n">
         <f aca="false">I56+1</f>
         <v>43</v>
       </c>
-      <c r="J57" s="28" t="str">
+      <c r="J57" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I57)</f>
         <v>Q43</v>
       </c>
-      <c r="K57" s="29" t="str">
+      <c r="K57" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J57,E57,H57)</f>
-        <v>Q43;;1</v>
+        <v>Q43;Yes;1</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="D58" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" s="32" t="n">
+      <c r="B58" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C58" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D58" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="E58" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="30" t="n">
         <f aca="false">I57+1</f>
         <v>44</v>
       </c>
-      <c r="J58" s="33" t="str">
+      <c r="J58" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I58)</f>
         <v>Q44</v>
       </c>
-      <c r="K58" s="31" t="str">
+      <c r="K58" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J58,E58,H58)</f>
-        <v>Q44;;1</v>
+        <v>Q44;Yes;1</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="40"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
-      <c r="H59" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" s="29" t="n">
+      <c r="B59" s="37"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="27" t="n">
         <f aca="false">I58+1</f>
         <v>45</v>
       </c>
-      <c r="J59" s="28" t="str">
+      <c r="J59" s="26" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I59)</f>
         <v>Q45</v>
       </c>
-      <c r="K59" s="29" t="str">
+      <c r="K59" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J59,E59,H59)</f>
-        <v>Q45;;1</v>
+        <v>Q45;Yes;1</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="40"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" s="32" t="n">
+      <c r="B60" s="37"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="E60" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="30" t="n">
         <f aca="false">I59+1</f>
         <v>46</v>
       </c>
-      <c r="J60" s="33" t="str">
+      <c r="J60" s="31" t="str">
         <f aca="false">_xlfn.CONCAT("Q",I60)</f>
         <v>Q46</v>
       </c>
-      <c r="K60" s="31" t="str">
+      <c r="K60" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J60,E60,H60)</f>
-        <v>Q46;;1</v>
+        <v>Q46;Yes;1</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/DRM Rapid Screening Tool - Questionnaire.xlsx
+++ b/data/DRM Rapid Screening Tool - Questionnaire.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="80">
   <si>
     <t xml:space="preserve">Evaluating Disaster Risk Management Policy Frameworks: A Rapid Screening Tool</t>
   </si>
@@ -87,9 +87,6 @@
     <t xml:space="preserve">Is there a legal framework (e.g., a DRM law or other legally-binding instruments) defining distinct responsibilities for disaster risk reduction and emergency management?</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Have any implementing decrees or regulations been approved since the adoption of the DRM legal framework? (e.g., rules on the structure or functions of the DRM agency or implementing regulations of the DRM law)</t>
   </si>
   <si>
@@ -181,9 +178,6 @@
   </si>
   <si>
     <t xml:space="preserve">Have any watershed basins undergone improvements in water management in the last four years?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partially</t>
   </si>
   <si>
     <t xml:space="preserve">4. Preparedness</t>
@@ -1067,7 +1061,7 @@
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="str">
         <f aca="false">IF(COUNTBLANK(E15:E60)&gt;0,_xlfn.CONCAT("Please complete the assessment to proceed. Remaining questions: ",COUNTBLANK(E15:E60)), _xlfn.TEXTJOIN("&amp;",FALSE(),K15:K60))</f>
-        <v>Q1;Yes;1&amp;Q2;Yes;1&amp;Q3;Yes;1&amp;Q4;Yes;1&amp;Q5;Yes;1&amp;Q6;Yes;1&amp;Q7;Yes;1&amp;Q8;Yes;1&amp;Q9;Yes;1&amp;Q10;Yes;1&amp;Q11;Yes;1&amp;Q12;Yes;1&amp;Q13;Yes;1&amp;Q14;Yes;1&amp;Q15;Yes;1&amp;Q16;Yes;1&amp;Q17;Yes;1&amp;Q18;Yes;0.25&amp;Q19;Yes;0.25&amp;Q20;Yes;0.25&amp;Q21;Yes;0.25&amp;Q22;Yes;1&amp;Q23;Yes;1&amp;Q24;Yes;1&amp;Q25;Yes;1&amp;Q26;Partially;1&amp;Q27;Partially;1&amp;Q28;Yes;1&amp;Q29;Yes;1&amp;Q30;Yes;1&amp;Q31;Yes;1&amp;Q32;Yes;1&amp;Q33;Yes;1&amp;Q34;Yes;1&amp;Q35;Yes;1&amp;Q36;Yes;1&amp;Q37;Yes;1&amp;Q38;Yes;1&amp;Q39;Yes;1&amp;Q40;Yes;1&amp;Q41;Yes;1&amp;Q42;Yes;1&amp;Q43;Yes;1&amp;Q44;Yes;1&amp;Q45;Yes;1&amp;Q46;Yes;1</v>
+        <v>Please complete the assessment to proceed. Remaining questions: 46</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="20"/>
@@ -1175,9 +1169,7 @@
       <c r="D15" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>21</v>
-      </c>
+      <c r="E15" s="26"/>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
       <c r="H15" s="26" t="n">
@@ -1192,18 +1184,16 @@
       </c>
       <c r="K15" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J15,E15,H15)</f>
-        <v>Q1;Yes;1</v>
+        <v>Q1;;1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
       <c r="D16" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="29" t="s">
         <v>21</v>
       </c>
+      <c r="E16" s="29"/>
       <c r="F16" s="29"/>
       <c r="G16" s="29"/>
       <c r="H16" s="30" t="n">
@@ -1219,7 +1209,7 @@
       </c>
       <c r="K16" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J16,E16,H16)</f>
-        <v>Q2;Yes;1</v>
+        <v>Q2;;1</v>
       </c>
       <c r="L16" s="32"/>
     </row>
@@ -1227,11 +1217,9 @@
       <c r="B17" s="24"/>
       <c r="C17" s="24"/>
       <c r="D17" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E17" s="26"/>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
       <c r="H17" s="26" t="n">
@@ -1247,18 +1235,16 @@
       </c>
       <c r="K17" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J17,E17,H17)</f>
-        <v>Q3;Yes;1</v>
+        <v>Q3;;1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="24"/>
       <c r="C18" s="24"/>
       <c r="D18" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E18" s="29"/>
       <c r="F18" s="29"/>
       <c r="G18" s="29"/>
       <c r="H18" s="30" t="n">
@@ -1274,20 +1260,18 @@
       </c>
       <c r="K18" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J18,E18,H18)</f>
-        <v>Q4;Yes;1</v>
+        <v>Q4;;1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="24"/>
       <c r="C19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>21</v>
-      </c>
+      <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
       <c r="H19" s="26" t="n">
@@ -1303,18 +1287,16 @@
       </c>
       <c r="K19" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J19,E19,H19)</f>
-        <v>Q5;Yes;1</v>
+        <v>Q5;;1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
       <c r="D20" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E20" s="29"/>
       <c r="F20" s="29"/>
       <c r="G20" s="29"/>
       <c r="H20" s="30" t="n">
@@ -1330,23 +1312,21 @@
       </c>
       <c r="K20" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J20,E20,H20)</f>
-        <v>Q6;Yes;1</v>
+        <v>Q6;;1</v>
       </c>
       <c r="L20" s="33"/>
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>21</v>
-      </c>
+      <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
       <c r="H21" s="26" t="n">
@@ -1362,18 +1342,16 @@
       </c>
       <c r="K21" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J21,E21,H21)</f>
-        <v>Q7;Yes;1</v>
+        <v>Q7;;1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="24"/>
       <c r="C22" s="24"/>
       <c r="D22" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E22" s="29"/>
       <c r="F22" s="29"/>
       <c r="G22" s="29"/>
       <c r="H22" s="30" t="n">
@@ -1389,18 +1367,16 @@
       </c>
       <c r="K22" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J22,E22,H22)</f>
-        <v>Q8;Yes;1</v>
+        <v>Q8;;1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="24"/>
       <c r="C23" s="24"/>
       <c r="D23" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E23" s="26"/>
       <c r="F23" s="26"/>
       <c r="G23" s="26"/>
       <c r="H23" s="26" t="n">
@@ -1416,7 +1392,7 @@
       </c>
       <c r="K23" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J23,E23,H23)</f>
-        <v>Q9;Yes;1</v>
+        <v>Q9;;1</v>
       </c>
       <c r="L23" s="32"/>
     </row>
@@ -1424,11 +1400,9 @@
       <c r="B24" s="24"/>
       <c r="C24" s="24"/>
       <c r="D24" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E24" s="29"/>
       <c r="F24" s="29"/>
       <c r="G24" s="29"/>
       <c r="H24" s="30" t="n">
@@ -1444,22 +1418,20 @@
       </c>
       <c r="K24" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J24,E24,H24)</f>
-        <v>Q10;Yes;1</v>
+        <v>Q10;;1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="D25" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>21</v>
-      </c>
+      <c r="E25" s="26"/>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
       <c r="H25" s="26" t="n">
@@ -1475,18 +1447,16 @@
       </c>
       <c r="K25" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J25,E25,H25)</f>
-        <v>Q11;Yes;1</v>
+        <v>Q11;;1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
       <c r="D26" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="E26" s="29"/>
       <c r="F26" s="29"/>
       <c r="G26" s="29"/>
       <c r="H26" s="30" t="n">
@@ -1502,18 +1472,16 @@
       </c>
       <c r="K26" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J26,E26,H26)</f>
-        <v>Q12;Yes;1</v>
+        <v>Q12;;1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="24"/>
       <c r="C27" s="24"/>
       <c r="D27" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E27" s="26"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
       <c r="H27" s="26" t="n">
@@ -1529,18 +1497,16 @@
       </c>
       <c r="K27" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J27,E27,H27)</f>
-        <v>Q13;Yes;1</v>
+        <v>Q13;;1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="24"/>
       <c r="C28" s="24"/>
       <c r="D28" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="E28" s="29"/>
       <c r="F28" s="29"/>
       <c r="G28" s="29"/>
       <c r="H28" s="30" t="n">
@@ -1556,21 +1522,19 @@
       </c>
       <c r="K28" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J28,E28,H28)</f>
-        <v>Q14;Yes;1</v>
+        <v>Q14;;1</v>
       </c>
       <c r="L28" s="32"/>
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="24"/>
       <c r="C29" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>21</v>
-      </c>
+      <c r="E29" s="26"/>
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
       <c r="H29" s="26" t="n">
@@ -1586,18 +1550,16 @@
       </c>
       <c r="K29" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J29,E29,H29)</f>
-        <v>Q15;Yes;1</v>
+        <v>Q15;;1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="24"/>
       <c r="C30" s="24"/>
       <c r="D30" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E30" s="29"/>
       <c r="F30" s="29"/>
       <c r="G30" s="29"/>
       <c r="H30" s="30" t="n">
@@ -1613,18 +1575,16 @@
       </c>
       <c r="K30" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J30,E30,H30)</f>
-        <v>Q16;Yes;1</v>
+        <v>Q16;;1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="24"/>
       <c r="C31" s="24"/>
       <c r="D31" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E31" s="26"/>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
       <c r="H31" s="26" t="n">
@@ -1640,21 +1600,19 @@
       </c>
       <c r="K31" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J31,E31,H31)</f>
-        <v>Q17;Yes;1</v>
+        <v>Q17;;1</v>
       </c>
       <c r="L31" s="34"/>
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="24"/>
       <c r="C32" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="29" t="s">
-        <v>21</v>
-      </c>
+      <c r="E32" s="29"/>
       <c r="F32" s="29"/>
       <c r="G32" s="29"/>
       <c r="H32" s="30" t="n">
@@ -1670,18 +1628,16 @@
       </c>
       <c r="K32" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J32,E32,H32)</f>
-        <v>Q18;Yes;0.25</v>
+        <v>Q18;;0.25</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="24"/>
       <c r="C33" s="24"/>
       <c r="D33" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="E33" s="26"/>
       <c r="F33" s="26"/>
       <c r="G33" s="26"/>
       <c r="H33" s="26" t="n">
@@ -1697,18 +1653,16 @@
       </c>
       <c r="K33" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J33,E33,H33)</f>
-        <v>Q19;Yes;0.25</v>
+        <v>Q19;;0.25</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="24"/>
       <c r="C34" s="24"/>
       <c r="D34" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E34" s="29"/>
       <c r="F34" s="29"/>
       <c r="G34" s="29"/>
       <c r="H34" s="30" t="n">
@@ -1724,18 +1678,16 @@
       </c>
       <c r="K34" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J34,E34,H34)</f>
-        <v>Q20;Yes;0.25</v>
+        <v>Q20;;0.25</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
       <c r="D35" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E35" s="26"/>
       <c r="F35" s="26"/>
       <c r="G35" s="26"/>
       <c r="H35" s="26" t="n">
@@ -1751,18 +1703,16 @@
       </c>
       <c r="K35" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J35,E35,H35)</f>
-        <v>Q21;Yes;0.25</v>
+        <v>Q21;;0.25</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
       <c r="D36" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E36" s="29"/>
       <c r="F36" s="29"/>
       <c r="G36" s="29"/>
       <c r="H36" s="30" t="n">
@@ -1778,18 +1728,16 @@
       </c>
       <c r="K36" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J36,E36,H36)</f>
-        <v>Q22;Yes;1</v>
+        <v>Q22;;1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="24"/>
       <c r="C37" s="24"/>
       <c r="D37" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="E37" s="26"/>
       <c r="F37" s="26"/>
       <c r="G37" s="26"/>
       <c r="H37" s="26" t="n">
@@ -1805,18 +1753,16 @@
       </c>
       <c r="K37" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J37,E37,H37)</f>
-        <v>Q23;Yes;1</v>
+        <v>Q23;;1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="24"/>
       <c r="C38" s="24"/>
       <c r="D38" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="E38" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="E38" s="29"/>
       <c r="F38" s="29"/>
       <c r="G38" s="29"/>
       <c r="H38" s="30" t="n">
@@ -1832,18 +1778,16 @@
       </c>
       <c r="K38" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J38,E38,H38)</f>
-        <v>Q24;Yes;1</v>
+        <v>Q24;;1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="24"/>
       <c r="C39" s="24"/>
       <c r="D39" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E39" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E39" s="26"/>
       <c r="F39" s="26"/>
       <c r="G39" s="26"/>
       <c r="H39" s="26" t="n">
@@ -1859,18 +1803,16 @@
       </c>
       <c r="K39" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J39,E39,H39)</f>
-        <v>Q25;Yes;1</v>
+        <v>Q25;;1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="24"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="E40" s="29" t="s">
-        <v>53</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="E40" s="29"/>
       <c r="F40" s="29"/>
       <c r="G40" s="29"/>
       <c r="H40" s="30" t="n">
@@ -1886,22 +1828,20 @@
       </c>
       <c r="K40" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J40,E40,H40)</f>
-        <v>Q26;Partially;1</v>
+        <v>Q26;;1</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>53</v>
-      </c>
+      <c r="E41" s="26"/>
       <c r="F41" s="26"/>
       <c r="G41" s="26"/>
       <c r="H41" s="27" t="n">
@@ -1917,18 +1857,16 @@
       </c>
       <c r="K41" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J41,E41,H41)</f>
-        <v>Q27;Partially;1</v>
+        <v>Q27;;1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="37"/>
       <c r="C42" s="24"/>
       <c r="D42" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="E42" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="E42" s="29"/>
       <c r="F42" s="29"/>
       <c r="G42" s="29"/>
       <c r="H42" s="31" t="n">
@@ -1944,18 +1882,16 @@
       </c>
       <c r="K42" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J42,E42,H42)</f>
-        <v>Q28;Yes;1</v>
+        <v>Q28;;1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="37"/>
       <c r="C43" s="24"/>
       <c r="D43" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="E43" s="26"/>
       <c r="F43" s="26"/>
       <c r="G43" s="26"/>
       <c r="H43" s="27" t="n">
@@ -1971,20 +1907,18 @@
       </c>
       <c r="K43" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J43,E43,H43)</f>
-        <v>Q29;Yes;1</v>
+        <v>Q29;;1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="37"/>
       <c r="C44" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D44" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E44" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="E44" s="29"/>
       <c r="F44" s="29"/>
       <c r="G44" s="29"/>
       <c r="H44" s="31" t="n">
@@ -2000,18 +1934,16 @@
       </c>
       <c r="K44" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J44,E44,H44)</f>
-        <v>Q30;Yes;1</v>
+        <v>Q30;;1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="37"/>
       <c r="C45" s="24"/>
       <c r="D45" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E45" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="E45" s="26"/>
       <c r="F45" s="26"/>
       <c r="G45" s="26"/>
       <c r="H45" s="27" t="n">
@@ -2027,18 +1959,16 @@
       </c>
       <c r="K45" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J45,E45,H45)</f>
-        <v>Q31;Yes;1</v>
+        <v>Q31;;1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="37"/>
       <c r="C46" s="24"/>
       <c r="D46" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E46" s="29"/>
       <c r="F46" s="29"/>
       <c r="G46" s="29"/>
       <c r="H46" s="31" t="n">
@@ -2054,18 +1984,16 @@
       </c>
       <c r="K46" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J46,E46,H46)</f>
-        <v>Q32;Yes;1</v>
+        <v>Q32;;1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="37"/>
       <c r="C47" s="24"/>
       <c r="D47" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="E47" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="E47" s="26"/>
       <c r="F47" s="26"/>
       <c r="G47" s="26"/>
       <c r="H47" s="27" t="n">
@@ -2081,20 +2009,18 @@
       </c>
       <c r="K47" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J47,E47,H47)</f>
-        <v>Q33;Yes;1</v>
+        <v>Q33;;1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="37"/>
       <c r="C48" s="24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="E48" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="E48" s="29"/>
       <c r="F48" s="29"/>
       <c r="G48" s="29"/>
       <c r="H48" s="31" t="n">
@@ -2110,18 +2036,16 @@
       </c>
       <c r="K48" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J48,E48,H48)</f>
-        <v>Q34;Yes;1</v>
+        <v>Q34;;1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="37"/>
       <c r="C49" s="24"/>
       <c r="D49" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="E49" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E49" s="26"/>
       <c r="F49" s="26"/>
       <c r="G49" s="26"/>
       <c r="H49" s="27" t="n">
@@ -2137,18 +2061,16 @@
       </c>
       <c r="K49" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J49,E49,H49)</f>
-        <v>Q35;Yes;1</v>
+        <v>Q35;;1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="37"/>
       <c r="C50" s="24"/>
       <c r="D50" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="E50" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="E50" s="29"/>
       <c r="F50" s="29"/>
       <c r="G50" s="29"/>
       <c r="H50" s="31" t="n">
@@ -2164,22 +2086,20 @@
       </c>
       <c r="K50" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J50,E50,H50)</f>
-        <v>Q36;Yes;1</v>
+        <v>Q36;;1</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="C51" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D51" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="E51" s="26" t="s">
-        <v>21</v>
-      </c>
+      <c r="E51" s="26"/>
       <c r="F51" s="26"/>
       <c r="G51" s="26"/>
       <c r="H51" s="27" t="n">
@@ -2195,18 +2115,16 @@
       </c>
       <c r="K51" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J51,E51,H51)</f>
-        <v>Q37;Yes;1</v>
+        <v>Q37;;1</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="37"/>
       <c r="C52" s="24"/>
       <c r="D52" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="E52" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E52" s="29"/>
       <c r="F52" s="29"/>
       <c r="G52" s="29"/>
       <c r="H52" s="31" t="n">
@@ -2222,18 +2140,16 @@
       </c>
       <c r="K52" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J52,E52,H52)</f>
-        <v>Q38;Yes;1</v>
+        <v>Q38;;1</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="37"/>
       <c r="C53" s="24"/>
       <c r="D53" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="E53" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E53" s="26"/>
       <c r="F53" s="26"/>
       <c r="G53" s="26"/>
       <c r="H53" s="27" t="n">
@@ -2249,18 +2165,16 @@
       </c>
       <c r="K53" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J53,E53,H53)</f>
-        <v>Q39;Yes;1</v>
+        <v>Q39;;1</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="37"/>
       <c r="C54" s="24"/>
       <c r="D54" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="E54" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="E54" s="29"/>
       <c r="F54" s="29"/>
       <c r="G54" s="29"/>
       <c r="H54" s="31" t="n">
@@ -2276,20 +2190,18 @@
       </c>
       <c r="K54" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J54,E54,H54)</f>
-        <v>Q40;Yes;1</v>
+        <v>Q40;;1</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="37"/>
       <c r="C55" s="24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="E55" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="E55" s="26"/>
       <c r="F55" s="26"/>
       <c r="G55" s="26"/>
       <c r="H55" s="27" t="n">
@@ -2305,18 +2217,16 @@
       </c>
       <c r="K55" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J55,E55,H55)</f>
-        <v>Q41;Yes;1</v>
+        <v>Q41;;1</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="37"/>
       <c r="C56" s="24"/>
       <c r="D56" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="E56" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="E56" s="29"/>
       <c r="F56" s="29"/>
       <c r="G56" s="29"/>
       <c r="H56" s="31" t="n">
@@ -2332,18 +2242,16 @@
       </c>
       <c r="K56" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J56,E56,H56)</f>
-        <v>Q42;Yes;1</v>
+        <v>Q42;;1</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="37"/>
       <c r="C57" s="24"/>
       <c r="D57" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="E57" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="E57" s="26"/>
       <c r="F57" s="26"/>
       <c r="G57" s="26"/>
       <c r="H57" s="27" t="n">
@@ -2359,22 +2267,20 @@
       </c>
       <c r="K57" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J57,E57,H57)</f>
-        <v>Q43;Yes;1</v>
+        <v>Q43;;1</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D58" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="E58" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="E58" s="29"/>
       <c r="F58" s="29"/>
       <c r="G58" s="29"/>
       <c r="H58" s="31" t="n">
@@ -2390,18 +2296,16 @@
       </c>
       <c r="K58" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J58,E58,H58)</f>
-        <v>Q44;Yes;1</v>
+        <v>Q44;;1</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="37"/>
       <c r="C59" s="37"/>
       <c r="D59" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E59" s="26" t="s">
-        <v>21</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="E59" s="26"/>
       <c r="F59" s="26"/>
       <c r="G59" s="26"/>
       <c r="H59" s="27" t="n">
@@ -2417,18 +2321,16 @@
       </c>
       <c r="K59" s="27" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J59,E59,H59)</f>
-        <v>Q45;Yes;1</v>
+        <v>Q45;;1</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="37"/>
       <c r="C60" s="37"/>
       <c r="D60" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="E60" s="29" t="s">
-        <v>21</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="E60" s="29"/>
       <c r="F60" s="29"/>
       <c r="G60" s="29"/>
       <c r="H60" s="31" t="n">
@@ -2444,7 +2346,7 @@
       </c>
       <c r="K60" s="30" t="str">
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J60,E60,H60)</f>
-        <v>Q46;Yes;1</v>
+        <v>Q46;;1</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2606,13 +2508,17 @@
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="C58:C60"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E15:G15 E17:G17 E19:G19 E21:G21 E23:G23 E25:G25 E27:G27 E29:G29 E31:G31 E33:G33 E35:G35 E37:G37 E39:G39 E41:G41 E43:G43 E45:G45 E47:G47 E49:G49 E51:G51 E53:G53 E55:G55 E57:G57 E59:G59" type="list">
+  <dataValidations count="3">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E15 E17 E19 E21 E23 E25 E27 E29 E31 E33 E35 E37 E39 E41 E43 E45 E47 E49 E51 E53 E55 E57 E59" type="list">
       <formula1>"Yes,No,Partially,Unknown"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E16:G16 E18:G18 E20:G20 E22:G22 E24:G24 E26:G26 E28:G28 E30:G30 E32:G32 E34:G34 E36:G36 E38:G38 E40:G40 E42:G42 E44:G44 E46:G46 E48:G48 E50:G50 E52:G52 E54:G54 E56:G56 E58:G58 E60:G60" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E16 E18 E20 E22 E24 E26 E28 E30 E32 E34 E36 E38 E40 E42 E44 E46 E48 E50 E52 E54 E56 E58 E60" type="list">
       <formula1>"Yes,No,Partially,Unknown"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="F15:G60" type="none">
+      <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/data/DRM Rapid Screening Tool - Questionnaire.xlsx
+++ b/data/DRM Rapid Screening Tool - Questionnaire.xlsx
@@ -474,7 +474,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -588,7 +588,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -609,6 +609,10 @@
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1348,7 +1352,7 @@
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="24"/>
       <c r="C22" s="24"/>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="34" t="s">
         <v>29</v>
       </c>
       <c r="E22" s="29"/>
@@ -1602,7 +1606,7 @@
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J31,E31,H31)</f>
         <v>Q17;;1</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="35"/>
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="24"/>
@@ -1634,7 +1638,7 @@
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="24"/>
       <c r="C33" s="24"/>
-      <c r="D33" s="35" t="s">
+      <c r="D33" s="36" t="s">
         <v>44</v>
       </c>
       <c r="E33" s="26"/>
@@ -1659,7 +1663,7 @@
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="24"/>
       <c r="C34" s="24"/>
-      <c r="D34" s="36" t="s">
+      <c r="D34" s="37" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="29"/>
@@ -1684,7 +1688,7 @@
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="36" t="s">
         <v>46</v>
       </c>
       <c r="E35" s="26"/>
@@ -1832,13 +1836,13 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="37" t="s">
+      <c r="B41" s="38" t="s">
         <v>52</v>
       </c>
       <c r="C41" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D41" s="38" t="s">
+      <c r="D41" s="39" t="s">
         <v>54</v>
       </c>
       <c r="E41" s="26"/>
@@ -1861,9 +1865,9 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="37"/>
+      <c r="B42" s="38"/>
       <c r="C42" s="24"/>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="40" t="s">
         <v>55</v>
       </c>
       <c r="E42" s="29"/>
@@ -1886,9 +1890,9 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="37"/>
+      <c r="B43" s="38"/>
       <c r="C43" s="24"/>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="39" t="s">
         <v>56</v>
       </c>
       <c r="E43" s="26"/>
@@ -1911,11 +1915,11 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="37"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="D44" s="39" t="s">
+      <c r="D44" s="40" t="s">
         <v>58</v>
       </c>
       <c r="E44" s="29"/>
@@ -1938,9 +1942,9 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="37"/>
+      <c r="B45" s="38"/>
       <c r="C45" s="24"/>
-      <c r="D45" s="38" t="s">
+      <c r="D45" s="39" t="s">
         <v>59</v>
       </c>
       <c r="E45" s="26"/>
@@ -1963,9 +1967,9 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="37"/>
+      <c r="B46" s="38"/>
       <c r="C46" s="24"/>
-      <c r="D46" s="39" t="s">
+      <c r="D46" s="40" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="29"/>
@@ -1988,9 +1992,9 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="37"/>
+      <c r="B47" s="38"/>
       <c r="C47" s="24"/>
-      <c r="D47" s="38" t="s">
+      <c r="D47" s="39" t="s">
         <v>61</v>
       </c>
       <c r="E47" s="26"/>
@@ -2013,11 +2017,11 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="37"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="39" t="s">
+      <c r="D48" s="40" t="s">
         <v>63</v>
       </c>
       <c r="E48" s="29"/>
@@ -2040,9 +2044,9 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="37"/>
+      <c r="B49" s="38"/>
       <c r="C49" s="24"/>
-      <c r="D49" s="38" t="s">
+      <c r="D49" s="39" t="s">
         <v>64</v>
       </c>
       <c r="E49" s="26"/>
@@ -2065,9 +2069,9 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="37"/>
+      <c r="B50" s="38"/>
       <c r="C50" s="24"/>
-      <c r="D50" s="39" t="s">
+      <c r="D50" s="40" t="s">
         <v>65</v>
       </c>
       <c r="E50" s="29"/>
@@ -2090,13 +2094,13 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="37" t="s">
+      <c r="B51" s="38" t="s">
         <v>66</v>
       </c>
       <c r="C51" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="D51" s="38" t="s">
+      <c r="D51" s="39" t="s">
         <v>68</v>
       </c>
       <c r="E51" s="26"/>
@@ -2119,9 +2123,9 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="37"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="24"/>
-      <c r="D52" s="39" t="s">
+      <c r="D52" s="40" t="s">
         <v>69</v>
       </c>
       <c r="E52" s="29"/>
@@ -2144,9 +2148,9 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="37"/>
+      <c r="B53" s="38"/>
       <c r="C53" s="24"/>
-      <c r="D53" s="38" t="s">
+      <c r="D53" s="39" t="s">
         <v>70</v>
       </c>
       <c r="E53" s="26"/>
@@ -2169,9 +2173,9 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="37"/>
+      <c r="B54" s="38"/>
       <c r="C54" s="24"/>
-      <c r="D54" s="39" t="s">
+      <c r="D54" s="40" t="s">
         <v>71</v>
       </c>
       <c r="E54" s="29"/>
@@ -2194,11 +2198,11 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="37"/>
+      <c r="B55" s="38"/>
       <c r="C55" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="D55" s="38" t="s">
+      <c r="D55" s="39" t="s">
         <v>73</v>
       </c>
       <c r="E55" s="26"/>
@@ -2221,9 +2225,9 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="37"/>
+      <c r="B56" s="38"/>
       <c r="C56" s="24"/>
-      <c r="D56" s="39" t="s">
+      <c r="D56" s="40" t="s">
         <v>74</v>
       </c>
       <c r="E56" s="29"/>
@@ -2246,9 +2250,9 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="37"/>
+      <c r="B57" s="38"/>
       <c r="C57" s="24"/>
-      <c r="D57" s="38" t="s">
+      <c r="D57" s="39" t="s">
         <v>75</v>
       </c>
       <c r="E57" s="26"/>
@@ -2271,13 +2275,13 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="37" t="s">
+      <c r="B58" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="C58" s="37" t="s">
+      <c r="C58" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="39" t="s">
+      <c r="D58" s="40" t="s">
         <v>77</v>
       </c>
       <c r="E58" s="29"/>
@@ -2300,9 +2304,9 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="37"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="38" t="s">
+      <c r="B59" s="38"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="39" t="s">
         <v>78</v>
       </c>
       <c r="E59" s="26"/>
@@ -2325,9 +2329,9 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="37"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="39" t="s">
+      <c r="B60" s="38"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="40" t="s">
         <v>79</v>
       </c>
       <c r="E60" s="29"/>

--- a/data/DRM Rapid Screening Tool - Questionnaire.xlsx
+++ b/data/DRM Rapid Screening Tool - Questionnaire.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Have any implementing decrees or regulations been approved since the adoption of the DRM legal framework? (e.g., rules on the structure or functions of the DRM agency or implementing regulations of the DRM law)</t>
   </si>
   <si>
-    <t xml:space="preserve">In the last 4 years, have DRM policy instruments reflecting progress towards the objective laid out in the DRM legal framework been officially approved/updated? (e.g., DRM strategies or policies) </t>
+    <t xml:space="preserve">In the last 5 years, have DRM policy instruments reflecting progress towards the objective laid out in the DRM legal framework been officially approved/updated? (e.g., DRM strategies or policies) </t>
   </si>
   <si>
     <t xml:space="preserve">Did the institution responsible for coordinating or leading DRM activities receive dedicated and significant funding for these functions in the last fiscal year? </t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Do guidelines or procedures for managing housing/settlements located in high-risk areas exist?</t>
   </si>
   <si>
-    <t xml:space="preserve">In the past 4 years, has risk information (e.g., hazard maps, risk assessments) consistently informed the elaboration of territorial, spatial, land use or urban planning instruments? (e.g., more than 50% of urban plans approved include risk considerations)</t>
+    <t xml:space="preserve">In the past 5 years, has risk information (e.g., hazard maps, risk assessments) consistently informed the elaboration of territorial, spatial, land use or urban planning instruments? (e.g., more than 50% of urban plans approved include risk considerations)</t>
   </si>
   <si>
     <t xml:space="preserve">3.2. Public investment at the central level</t>
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Is there at least one legally binding building code or standard that requires earthquake-resistant or other hazard-resistant (e.g., wind, flood) design for buildings?</t>
   </si>
   <si>
-    <t xml:space="preserve">In the past 4 years, has any public project or program been allocated funding for retrofitting activities that follow vulnerability assessments and resilient design standards?</t>
+    <t xml:space="preserve">In the past 5 years, has any public project or program been allocated funding for retrofitting activities that follow vulnerability assessments and resilient design standards?</t>
   </si>
   <si>
     <t xml:space="preserve">Is there a legal framework for water supply and sanitation in urban areas that take flood risk into account?</t>
@@ -177,7 +177,7 @@
     <t xml:space="preserve">Is there a water governance framework that includes a coordination mechanism gathering the main actors in charge of Integrated Water Resources Management (e.g., water, agriculture, urban planning, energy)?</t>
   </si>
   <si>
-    <t xml:space="preserve">Have any watershed basins undergone improvements in water management in the last four years?</t>
+    <t xml:space="preserve">Have any watershed basins undergone improvements in water management in the last 5 years?</t>
   </si>
   <si>
     <t xml:space="preserve">4. Preparedness</t>
@@ -192,7 +192,7 @@
     <t xml:space="preserve">Over the most recent major disaster, was the population promptly alerted (e.g., via SMS or other tailored communication channels)? </t>
   </si>
   <si>
-    <t xml:space="preserve">In the past 4 years, has there been a consistent budget allocation for the expansion, maintenance, and operation of the geophysical and/or hydrometeorological network?</t>
+    <t xml:space="preserve">In the past 5 years, has there been a consistent budget allocation for the expansion, maintenance, and operation of the geophysical and/or hydrometeorological network?</t>
   </si>
   <si>
     <t xml:space="preserve">4.2. Emergency Preparedness and Response (EP&amp;R)</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Are there regulations that define standards for catastrophe insurance coverage of public or private assets?</t>
   </si>
   <si>
-    <t xml:space="preserve">In the past 4 years, has the $ amount of financing that can be mobilized through sovereign risk financing instruments increased?</t>
+    <t xml:space="preserve">In the past 5 years, has the $ amount of financing that can be mobilized through sovereign risk financing instruments increased?</t>
   </si>
   <si>
     <t xml:space="preserve">6. Resilient Reconstruction</t>

--- a/data/DRM Rapid Screening Tool - Questionnaire.xlsx
+++ b/data/DRM Rapid Screening Tool - Questionnaire.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Does the National Development Strategy (or equivalent national planning instrument) contain objectives, targets or indicators related to DRM / DRR?</t>
   </si>
   <si>
-    <t xml:space="preserve">Have at least 4 essential government entities* included explicit DRM/ DRR targets and indicators in their most recent strategic planning documents? (e.g., Ministry of Health Strategic Plan, National Education Strategy/Policy, National Water and Sanitation Master Plan, Transport Infrastructure Development Plan)</t>
+    <t xml:space="preserve">Have at least 4 essential government entities* included explicit DRM/ DRR targets and indicators in their most recent strategic planning documents? (e.g., Ministry of Health Strategic Plan, National Education Strategy/Policy, Tourism Policy, National Water and Sanitation Master Plan, Transport Infrastructure Development Plan)</t>
   </si>
   <si>
     <t xml:space="preserve">2. Risk Identification</t>
@@ -141,10 +141,11 @@
     <t xml:space="preserve">3.2. Public investment at the central level</t>
   </si>
   <si>
-    <t xml:space="preserve">Do laws and regulations mandate disaster and climate risk screening as part of the appraisal of new public investment projects?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do official guidelines exist defining disaster and climate risk screening methodologies for new public investment projects? </t>
+    <t xml:space="preserve">Do laws and regulations mandate disaster and climate risk screening as part of the appraisal of new public investment projects, including new Public-Private Partnerships?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the government provide incentives for private-sector actors (including tourism, retail, and property businesses) to invest in disaster-resilient infrastructure or business continuity planning?
+Examples of such incentives may include the promotion of business continuity planning, resilience standards linked to financing mechanisms, tax incentives, subsidies, or other forms of financial support.</t>
   </si>
   <si>
     <t xml:space="preserve">Are approved projects that have been identified as high-risk (or equivalent) through the disaster and climate screening process required to include risk mitigation measures?</t>
@@ -271,7 +272,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,6 +374,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -474,7 +481,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -613,6 +620,10 @@
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -898,7 +909,7 @@
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="89.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="31.44"/>
@@ -1560,7 +1571,7 @@
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="24"/>
       <c r="C30" s="24"/>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="35" t="s">
         <v>40</v>
       </c>
       <c r="E30" s="29"/>
@@ -1606,7 +1617,7 @@
         <f aca="false">_xlfn.TEXTJOIN(";",FALSE(),J31,E31,H31)</f>
         <v>Q17;;1</v>
       </c>
-      <c r="L31" s="35"/>
+      <c r="L31" s="36"/>
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="24"/>
@@ -1638,7 +1649,7 @@
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="24"/>
       <c r="C33" s="24"/>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="37" t="s">
         <v>44</v>
       </c>
       <c r="E33" s="26"/>
@@ -1663,7 +1674,7 @@
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="24"/>
       <c r="C34" s="24"/>
-      <c r="D34" s="37" t="s">
+      <c r="D34" s="38" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="29"/>
@@ -1688,7 +1699,7 @@
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="37" t="s">
         <v>46</v>
       </c>
       <c r="E35" s="26"/>
@@ -1836,13 +1847,13 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="38" t="s">
+      <c r="B41" s="39" t="s">
         <v>52</v>
       </c>
       <c r="C41" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D41" s="39" t="s">
+      <c r="D41" s="40" t="s">
         <v>54</v>
       </c>
       <c r="E41" s="26"/>
@@ -1865,9 +1876,9 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="38"/>
+      <c r="B42" s="39"/>
       <c r="C42" s="24"/>
-      <c r="D42" s="40" t="s">
+      <c r="D42" s="41" t="s">
         <v>55</v>
       </c>
       <c r="E42" s="29"/>
@@ -1890,9 +1901,9 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="38"/>
+      <c r="B43" s="39"/>
       <c r="C43" s="24"/>
-      <c r="D43" s="39" t="s">
+      <c r="D43" s="40" t="s">
         <v>56</v>
       </c>
       <c r="E43" s="26"/>
@@ -1915,11 +1926,11 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="38"/>
+      <c r="B44" s="39"/>
       <c r="C44" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="D44" s="40" t="s">
+      <c r="D44" s="41" t="s">
         <v>58</v>
       </c>
       <c r="E44" s="29"/>
@@ -1942,9 +1953,9 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="38"/>
+      <c r="B45" s="39"/>
       <c r="C45" s="24"/>
-      <c r="D45" s="39" t="s">
+      <c r="D45" s="40" t="s">
         <v>59</v>
       </c>
       <c r="E45" s="26"/>
@@ -1967,9 +1978,9 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="38"/>
+      <c r="B46" s="39"/>
       <c r="C46" s="24"/>
-      <c r="D46" s="40" t="s">
+      <c r="D46" s="41" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="29"/>
@@ -1992,9 +2003,9 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="38"/>
+      <c r="B47" s="39"/>
       <c r="C47" s="24"/>
-      <c r="D47" s="39" t="s">
+      <c r="D47" s="40" t="s">
         <v>61</v>
       </c>
       <c r="E47" s="26"/>
@@ -2017,11 +2028,11 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="38"/>
+      <c r="B48" s="39"/>
       <c r="C48" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="40" t="s">
+      <c r="D48" s="41" t="s">
         <v>63</v>
       </c>
       <c r="E48" s="29"/>
@@ -2044,9 +2055,9 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="38"/>
+      <c r="B49" s="39"/>
       <c r="C49" s="24"/>
-      <c r="D49" s="39" t="s">
+      <c r="D49" s="40" t="s">
         <v>64</v>
       </c>
       <c r="E49" s="26"/>
@@ -2069,9 +2080,9 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="38"/>
+      <c r="B50" s="39"/>
       <c r="C50" s="24"/>
-      <c r="D50" s="40" t="s">
+      <c r="D50" s="41" t="s">
         <v>65</v>
       </c>
       <c r="E50" s="29"/>
@@ -2094,13 +2105,13 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="38" t="s">
+      <c r="B51" s="39" t="s">
         <v>66</v>
       </c>
       <c r="C51" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="D51" s="39" t="s">
+      <c r="D51" s="40" t="s">
         <v>68</v>
       </c>
       <c r="E51" s="26"/>
@@ -2123,9 +2134,9 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="38"/>
+      <c r="B52" s="39"/>
       <c r="C52" s="24"/>
-      <c r="D52" s="40" t="s">
+      <c r="D52" s="41" t="s">
         <v>69</v>
       </c>
       <c r="E52" s="29"/>
@@ -2148,9 +2159,9 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="38"/>
+      <c r="B53" s="39"/>
       <c r="C53" s="24"/>
-      <c r="D53" s="39" t="s">
+      <c r="D53" s="40" t="s">
         <v>70</v>
       </c>
       <c r="E53" s="26"/>
@@ -2173,9 +2184,9 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="38"/>
+      <c r="B54" s="39"/>
       <c r="C54" s="24"/>
-      <c r="D54" s="40" t="s">
+      <c r="D54" s="41" t="s">
         <v>71</v>
       </c>
       <c r="E54" s="29"/>
@@ -2198,11 +2209,11 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="38"/>
+      <c r="B55" s="39"/>
       <c r="C55" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="D55" s="39" t="s">
+      <c r="D55" s="40" t="s">
         <v>73</v>
       </c>
       <c r="E55" s="26"/>
@@ -2225,9 +2236,9 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="38"/>
+      <c r="B56" s="39"/>
       <c r="C56" s="24"/>
-      <c r="D56" s="40" t="s">
+      <c r="D56" s="41" t="s">
         <v>74</v>
       </c>
       <c r="E56" s="29"/>
@@ -2250,9 +2261,9 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="38"/>
+      <c r="B57" s="39"/>
       <c r="C57" s="24"/>
-      <c r="D57" s="39" t="s">
+      <c r="D57" s="40" t="s">
         <v>75</v>
       </c>
       <c r="E57" s="26"/>
@@ -2275,13 +2286,13 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="38" t="s">
+      <c r="B58" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="C58" s="38" t="s">
+      <c r="C58" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="40" t="s">
+      <c r="D58" s="41" t="s">
         <v>77</v>
       </c>
       <c r="E58" s="29"/>
@@ -2304,9 +2315,9 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="38"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="39" t="s">
+      <c r="B59" s="39"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="40" t="s">
         <v>78</v>
       </c>
       <c r="E59" s="26"/>
@@ -2329,9 +2340,9 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="38"/>
-      <c r="C60" s="38"/>
-      <c r="D60" s="40" t="s">
+      <c r="B60" s="39"/>
+      <c r="C60" s="39"/>
+      <c r="D60" s="41" t="s">
         <v>79</v>
       </c>
       <c r="E60" s="29"/>

--- a/data/DRM Rapid Screening Tool - Questionnaire.xlsx
+++ b/data/DRM Rapid Screening Tool - Questionnaire.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="80">
   <si>
-    <t xml:space="preserve">Evaluating Disaster Risk Management Policy Frameworks: A Rapid Screening Tool</t>
+    <t xml:space="preserve">Evaluating Disaster Risk Management Policy Frameworks: A DRM Policy Diagnostic Tool</t>
   </si>
   <si>
     <t xml:space="preserve">Instructions</t>
@@ -272,7 +272,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,12 +374,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -622,7 +616,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2502,8 +2496,7 @@
     <row r="196" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="197" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B2:H2"/>
+  <mergeCells count="18">
     <mergeCell ref="B15:B20"/>
     <mergeCell ref="C15:C18"/>
     <mergeCell ref="C19:C20"/>

--- a/data/DRM Rapid Screening Tool - Questionnaire.xlsx
+++ b/data/DRM Rapid Screening Tool - Questionnaire.xlsx
@@ -141,10 +141,10 @@
     <t xml:space="preserve">3.2. Public investment at the central level</t>
   </si>
   <si>
-    <t xml:space="preserve">Do laws and regulations mandate disaster and climate risk screening as part of the appraisal of new public investment projects, including new Public-Private Partnerships?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does the government provide incentives for private-sector actors (including tourism, retail, and property businesses) to invest in disaster-resilient infrastructure or business continuity planning?
+    <t xml:space="preserve">Do laws and regulations mandate disaster and climate risk screening as part of the appraisal of public investment projects, including Public-Private Partnerships?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the government provide incentives for private-sector actors (including tourism, retail, and property businesses) to invest in disaster-resilient infrastructure and/or business continuity planning?
 Examples of such incentives may include the promotion of business continuity planning, resilience standards linked to financing mechanisms, tax incentives, subsidies, or other forms of financial support.</t>
   </si>
   <si>
